--- a/ig/DM_FINESS_New/ValueSet-jdv-j314-engagement-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j314-engagement-finess.xlsx
@@ -102,7 +102,7 @@
     <t>=</t>
   </si>
   <si>
-    <t>2</t>
+    <t>1</t>
   </si>
   <si>
     <t/>

--- a/ig/DM_FINESS_New/ValueSet-jdv-j314-engagement-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j314-engagement-finess.xlsx
@@ -102,7 +102,7 @@
     <t>=</t>
   </si>
   <si>
-    <t>1</t>
+    <t>2</t>
   </si>
   <si>
     <t/>

--- a/ig/DM_FINESS_New/ValueSet-jdv-j314-engagement-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j314-engagement-finess.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j293-type-engagement-finess</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j314-engagement-finess</t>
   </si>
   <si>
     <t>Identifier</t>
